--- a/docs/08-reports/test-reports/Report5.3_System_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.3_System_Test.xlsx
@@ -1194,7 +1194,7 @@
         <v>Issue Date</v>
       </c>
       <c r="F5" s="14" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -1222,8 +1222,8 @@
         <v>Document Code</v>
       </c>
       <c r="B6" s="16" t="str">
-        <f>B5&amp;"_"&amp;B2&amp;"_"&amp;F6</f>
-        <v>SEP490-G116_SYSTEM TEST REPORT DOCUMENT_1</v>
+        <f>B5&amp;"_"&amp;B2&amp;"_v"&amp;F6</f>
+        <v>SEP490-G116_SYSTEM TEST REPORT DOCUMENT_v1.1</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="6"/>
@@ -1231,7 +1231,7 @@
         <v>Version</v>
       </c>
       <c r="F6" s="17" t="str">
-        <v>1.0</v>
+        <v>1.1</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -1387,12 +1387,14 @@
       <c r="B11" s="26" t="str">
         <v>1.0</v>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="27" t="str">
+        <v>Report 5</v>
+      </c>
       <c r="D11" s="28" t="str">
         <v>A</v>
       </c>
       <c r="E11" s="29" t="str">
-        <v>Generate English test documentation from TrustCabinet source using the supplied template.</v>
+        <v>Generate test documents from source</v>
       </c>
       <c r="F11" s="30"/>
       <c r="G11" s="31"/>
@@ -1417,12 +1419,22 @@
       <c r="Z11" s="31"/>
     </row>
     <row r="12" ht="21.75" customHeight="1">
-      <c r="A12" s="32"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="33"/>
+      <c r="A12" s="32" t="str">
+        <v>2026-10-29</v>
+      </c>
+      <c r="B12" s="26" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="C12" s="27" t="str">
+        <v>Test cases</v>
+      </c>
+      <c r="D12" s="28" t="str">
+        <v>M</v>
+      </c>
+      <c r="E12" s="29" t="str">
+        <v>Regenerate: 1099 xUnit methods</v>
+      </c>
+      <c r="F12" s="33" t="str"/>
       <c r="G12" s="31"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
@@ -1754,7 +1766,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>Source-reviewed end-to-end workflow; record results only after execution.</v>
+        <v>System-level test flow: Isolate meeting data across roles</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -1794,7 +1806,7 @@
       <c r="N4" s="97"/>
       <c r="O4" s="99"/>
       <c r="P4" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
     </row>
     <row r="5">
@@ -2009,7 +2021,7 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="92" customHeight="1">
+    <row r="12" ht="109.5" customHeight="1">
       <c r="A12" s="108" t="str">
         <v>SYS-07</v>
       </c>
@@ -2019,23 +2031,19 @@
       <c r="C12" s="108" t="str">
         <v>1. Open list/details as each role.
 2. Try history, edit and transitions.
-3. Replace approver and retry as former
-approver.</v>
+3. Replace approver and retry as former approver.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>Access follows relationship/state;
-unrelated or revoked users cannot read
-restricted data; inaccessible records
-return 404.</v>
+        <v>1. Access follows relationship/state.
+2. Unrelated or revoked users cannot read restricted data.
+3. Inaccessible records return 404.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>Organizer, assigned approver,
-participant, outsider;
-Draft/WaitingApproval/Published
-fixtures.</v>
+        <v>1. Organizer, assigned approver, participant, outsider.
+2. Draft/WaitingApproval/Published fixtures.</v>
       </c>
       <c r="F12" s="108" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="G12" s="109" t="str"/>
       <c r="H12" s="108" t="str"/>
@@ -2045,11 +2053,7 @@
       <c r="L12" s="108" t="str"/>
       <c r="M12" s="109" t="str"/>
       <c r="N12" s="108" t="str"/>
-      <c r="O12" s="110" t="str">
-        <v>frontend/src/features/meeti
-ngs/detail/MeetingDetailPag
-e.tsx:1</v>
-      </c>
+      <c r="O12" s="110" t="str"/>
       <c r="P12"/>
     </row>
   </sheetData>
@@ -2131,7 +2135,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>Source-reviewed end-to-end workflow; record results only after execution.</v>
+        <v>System-level test flow: Recover queued email after SMTP outage</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -2171,7 +2175,7 @@
       <c r="N4" s="97"/>
       <c r="O4" s="99"/>
       <c r="P4" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
     </row>
     <row r="5">
@@ -2386,7 +2390,7 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="110" customHeight="1">
+    <row r="12" ht="95.0" customHeight="1">
       <c r="A12" s="108" t="str">
         <v>SYS-08</v>
       </c>
@@ -2401,16 +2405,16 @@
 5. Compare mail and queue.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>Publication persists; email retries
-after recovery without duplicate
-deduplication keys.</v>
+        <v>1. Publication persists.
+2. Email retries after recovery without duplicate deduplication keys.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>Isolated staging; controllable SMTP
-sandbox; valid Approved fixture.</v>
+        <v>1. Isolated staging.
+2. Controllable SMTP sandbox.
+3. Valid Approved fixture.</v>
       </c>
       <c r="F12" s="108" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="G12" s="109" t="str"/>
       <c r="H12" s="108" t="str"/>
@@ -2420,11 +2424,7 @@
       <c r="L12" s="108" t="str"/>
       <c r="M12" s="109" t="str"/>
       <c r="N12" s="108" t="str"/>
-      <c r="O12" s="110" t="str">
-        <v>backend/TrustCabinet.Infras
-tructure/Email/EmailDeliver
-yWorker.cs:1</v>
-      </c>
+      <c r="O12" s="110" t="str"/>
       <c r="P12"/>
     </row>
   </sheetData>
@@ -2506,7 +2506,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>Source-reviewed end-to-end workflow; record results only after execution.</v>
+        <v>System-level test flow: Operate agenda through complete meeting UI</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -2546,7 +2546,7 @@
       <c r="N4" s="97"/>
       <c r="O4" s="99"/>
       <c r="P4" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
     </row>
     <row r="5">
@@ -2761,13 +2761,12 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="92" customHeight="1">
+    <row r="12" ht="95.0" customHeight="1">
       <c r="A12" s="108" t="str">
         <v>SYS-09</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Operate agenda through complete meeting
-UI</v>
+        <v>Operate agenda through complete meeting UI</v>
       </c>
       <c r="C12" s="108" t="str">
         <v>1. Create/reorder agenda in UI.
@@ -2776,16 +2775,14 @@
 4. Observe participant browser.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>After integration, order/state/duration
-synchronize according to API; re-execute
-workflow.</v>
+        <v>1. After integration, order/state/duration synchronize according to API.
+2. Re-execute workflow.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>Blocked: agenda UI and meeting-start
-workflow unavailable in this checkout.</v>
+        <v>1. Blocked: agenda UI and meeting-start workflow unavailable in this checkout.</v>
       </c>
       <c r="F12" s="108" t="str">
-        <v>Blocked</v>
+        <v>Pending</v>
       </c>
       <c r="G12" s="109" t="str"/>
       <c r="H12" s="108" t="str"/>
@@ -2795,11 +2792,7 @@
       <c r="L12" s="108" t="str"/>
       <c r="M12" s="109" t="str"/>
       <c r="N12" s="108" t="str"/>
-      <c r="O12" s="110" t="str">
-        <v>frontend/src/features/meeti
-ngs/detail/MeetingDetailPag
-e.tsx:1</v>
-      </c>
+      <c r="O12" s="110" t="str"/>
       <c r="P12"/>
     </row>
   </sheetData>
@@ -3076,7 +3069,7 @@
       <c r="Y8" s="51"/>
       <c r="Z8" s="51"/>
     </row>
-    <row r="9" ht="85" customHeight="1">
+    <row r="9" ht="80.5" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="56" t="n">
         <v>1</v>
@@ -3091,7 +3084,10 @@
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F9" s="59" t="str">
-        <v>AdminUsers; MeetingCreator role; new user; staging PostgreSQL/Redis.</v>
+        <v>1. AdminUsers.
+2. MeetingCreator role.
+3. New user.
+4. Staging PostgreSQL/Redis.</v>
       </c>
       <c r="G9" s="60"/>
       <c r="H9" s="10"/>
@@ -3114,7 +3110,7 @@
       <c r="Y9" s="10"/>
       <c r="Z9" s="10"/>
     </row>
-    <row r="10" ht="85" customHeight="1">
+    <row r="10" ht="66.0" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="56" t="n">
         <v>2</v>
@@ -3129,7 +3125,9 @@
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F10" s="59" t="str">
-        <v>Separate active organizer/approver; ready meeting; notification worker.</v>
+        <v>1. Separate active organizer/approver.
+2. Ready meeting.
+3. Notification worker.</v>
       </c>
       <c r="G10" s="60"/>
       <c r="H10" s="10"/>
@@ -3152,7 +3150,7 @@
       <c r="Y10" s="10"/>
       <c r="Z10" s="10"/>
     </row>
-    <row r="11" ht="85" customHeight="1">
+    <row r="11" ht="95.0" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="56" t="n">
         <v>3</v>
@@ -3167,7 +3165,10 @@
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F11" s="59" t="str">
-        <v>Approved fixture with active Chair/Secretary and participants; seeded roster; SMTP sandbox; workers enabled.</v>
+        <v>1. Approved fixture with active Chair/Secretary and participants.
+2. Seeded roster.
+3. SMTP sandbox.
+4. Workers enabled.</v>
       </c>
       <c r="G11" s="60"/>
       <c r="H11" s="10"/>
@@ -3190,7 +3191,7 @@
       <c r="Y11" s="10"/>
       <c r="Z11" s="10"/>
     </row>
-    <row r="12" ht="85" customHeight="1">
+    <row r="12" ht="80.5" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="56" t="n">
         <v>4</v>
@@ -3205,7 +3206,10 @@
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F12" s="59" t="str">
-        <v>Published meeting; participants; original invitation recorded; SMTP sandbox.</v>
+        <v>1. Published meeting.
+2. Participants.
+3. Original invitation recorded.
+4. SMTP sandbox.</v>
       </c>
       <c r="G12" s="60"/>
       <c r="H12" s="10"/>
@@ -3228,7 +3232,7 @@
       <c r="Y12" s="10"/>
       <c r="Z12" s="10"/>
     </row>
-    <row r="13" ht="85" customHeight="1">
+    <row r="13" ht="66.0" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="56" t="n">
         <v>5</v>
@@ -3243,7 +3247,9 @@
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F13" s="59" t="str">
-        <v>Independent admin; target signed in on two tabs; not final admin.</v>
+        <v>1. Independent admin.
+2. Target signed in on two tabs.
+3. Not final admin.</v>
       </c>
       <c r="G13" s="60"/>
       <c r="H13" s="10"/>
@@ -3266,7 +3272,7 @@
       <c r="Y13" s="10"/>
       <c r="Z13" s="10"/>
     </row>
-    <row r="14" ht="85" customHeight="1">
+    <row r="14" ht="66.0" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="56" t="n">
         <v>6</v>
@@ -3281,7 +3287,9 @@
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F14" s="59" t="str">
-        <v>Administrator/test user; SMTP sandbox; issued reset link.</v>
+        <v>1. Administrator/test user.
+2. SMTP sandbox.
+3. Issued reset link.</v>
       </c>
       <c r="G14" s="60"/>
       <c r="H14" s="10"/>
@@ -3304,7 +3312,7 @@
       <c r="Y14" s="10"/>
       <c r="Z14" s="10"/>
     </row>
-    <row r="15" ht="85" customHeight="1">
+    <row r="15" ht="80.5" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="56" t="n">
         <v>7</v>
@@ -3319,7 +3327,8 @@
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F15" s="59" t="str">
-        <v>Organizer, assigned approver, participant, outsider; Draft/WaitingApproval/Published fixtures.</v>
+        <v>1. Organizer, assigned approver, participant, outsider.
+2. Draft/WaitingApproval/Published fixtures.</v>
       </c>
       <c r="G15" s="60"/>
       <c r="H15" s="10"/>
@@ -3342,7 +3351,7 @@
       <c r="Y15" s="10"/>
       <c r="Z15" s="10"/>
     </row>
-    <row r="16" ht="85" customHeight="1">
+    <row r="16" ht="66.0" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="56" t="n">
         <v>8</v>
@@ -3357,7 +3366,9 @@
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F16" s="59" t="str">
-        <v>Isolated staging; controllable SMTP sandbox; valid Approved fixture.</v>
+        <v>1. Isolated staging.
+2. Controllable SMTP sandbox.
+3. Valid Approved fixture.</v>
       </c>
       <c r="G16" s="60"/>
       <c r="H16" s="10"/>
@@ -3380,7 +3391,7 @@
       <c r="Y16" s="10"/>
       <c r="Z16" s="10"/>
     </row>
-    <row r="17" ht="85" customHeight="1">
+    <row r="17" ht="51.5" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="56" t="n">
         <v>9</v>
@@ -3395,7 +3406,7 @@
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F17" s="59" t="str">
-        <v>Blocked: agenda UI and meeting-start workflow unavailable in this checkout.</v>
+        <v>1. Blocked: agenda UI and meeting-start workflow unavailable in this checkout.</v>
       </c>
       <c r="G17" s="60"/>
       <c r="H17" s="10"/>
@@ -3428,15 +3439,15 @@
     <mergeCell ref="D5:F5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D9" location="'WorkFlow1'!A1"/>
-    <hyperlink ref="D10" location="'WorkFlow2'!A1"/>
-    <hyperlink ref="D11" location="'WorkFlow3'!A1"/>
-    <hyperlink ref="D12" location="'WorkFlow4'!A1"/>
-    <hyperlink ref="D13" location="'WorkFlow5'!A1"/>
-    <hyperlink ref="D14" location="'WorkFlow6'!A1"/>
-    <hyperlink ref="D15" location="'WorkFlow7'!A1"/>
-    <hyperlink ref="D16" location="'WorkFlow8'!A1"/>
-    <hyperlink ref="D17" location="'WorkFlow9'!A1"/>
+    <hyperlink ref="D9" location="'WorkFlow1'!A1" display="WorkFlow1"/>
+    <hyperlink ref="D10" location="'WorkFlow2'!A1" display="WorkFlow2"/>
+    <hyperlink ref="D11" location="'WorkFlow3'!A1" display="WorkFlow3"/>
+    <hyperlink ref="D12" location="'WorkFlow4'!A1" display="WorkFlow4"/>
+    <hyperlink ref="D13" location="'WorkFlow5'!A1" display="WorkFlow5"/>
+    <hyperlink ref="D14" location="'WorkFlow6'!A1" display="WorkFlow6"/>
+    <hyperlink ref="D15" location="'WorkFlow7'!A1" display="WorkFlow7"/>
+    <hyperlink ref="D16" location="'WorkFlow8'!A1" display="WorkFlow8"/>
+    <hyperlink ref="D17" location="'WorkFlow9'!A1" display="WorkFlow9"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.1506944444444445" footer="0.0" header="0.0" left="0.7479166666666667" right="0.7479166666666667" top="0.9840277777777778"/>
@@ -3606,7 +3617,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="71"/>
       <c r="H5" s="76" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-29</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
@@ -3627,14 +3638,12 @@
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="21.75" customHeight="1">
       <c r="A6" s="66"/>
       <c r="B6" s="74" t="str">
         <v>Notes</v>
       </c>
-      <c r="C6" s="77" t="str">
-        <v>Round 1. Pending: NotRun/Blocked/Partial. N/A: Skipped.</v>
-      </c>
+      <c r="C6" s="77" t="str"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4345,15 +4354,15 @@
     <mergeCell ref="C6:H6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C11" location="'WorkFlow1'!A1"/>
-    <hyperlink ref="C12" location="'WorkFlow2'!A1"/>
-    <hyperlink ref="C13" location="'WorkFlow3'!A1"/>
-    <hyperlink ref="C14" location="'WorkFlow4'!A1"/>
-    <hyperlink ref="C15" location="'WorkFlow5'!A1"/>
-    <hyperlink ref="C16" location="'WorkFlow6'!A1"/>
-    <hyperlink ref="C17" location="'WorkFlow7'!A1"/>
-    <hyperlink ref="C18" location="'WorkFlow8'!A1"/>
-    <hyperlink ref="C19" location="'WorkFlow9'!A1"/>
+    <hyperlink ref="C11" location="'WorkFlow1'!A1" display="WorkFlow1"/>
+    <hyperlink ref="C12" location="'WorkFlow2'!A1" display="WorkFlow2"/>
+    <hyperlink ref="C13" location="'WorkFlow3'!A1" display="WorkFlow3"/>
+    <hyperlink ref="C14" location="'WorkFlow4'!A1" display="WorkFlow4"/>
+    <hyperlink ref="C15" location="'WorkFlow5'!A1" display="WorkFlow5"/>
+    <hyperlink ref="C16" location="'WorkFlow6'!A1" display="WorkFlow6"/>
+    <hyperlink ref="C17" location="'WorkFlow7'!A1" display="WorkFlow7"/>
+    <hyperlink ref="C18" location="'WorkFlow8'!A1" display="WorkFlow8"/>
+    <hyperlink ref="C19" location="'WorkFlow9'!A1" display="WorkFlow9"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.9840277777777777" footer="0.0" header="0.0" left="0.7479166666666667" right="0.7479166666666667" top="0.9840277777777778"/>
@@ -4433,7 +4442,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>Source-reviewed end-to-end workflow; record results only after execution.</v>
+        <v>System-level test flow: Provision access, create a meeting and revoke permission</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -4473,7 +4482,7 @@
       <c r="N4" s="97"/>
       <c r="O4" s="99"/>
       <c r="P4" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
     </row>
     <row r="5">
@@ -4688,13 +4697,12 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="110" customHeight="1">
+    <row r="12" ht="95.0" customHeight="1">
       <c r="A12" s="108" t="str">
         <v>SYS-01</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Provision access, create a meeting and
-revoke permission</v>
+        <v>Provision access, create a meeting and revoke permission</v>
       </c>
       <c r="C12" s="108" t="str">
         <v>1. Create user and assign role.
@@ -4704,16 +4712,17 @@
 5. Reload and retry creation.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>Creation succeeds while authorized and
-fails after revocation; original Draft
-remains intact.</v>
+        <v>1. Creation succeeds while authorized and fails after revocation.
+2. Original Draft remains intact.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>AdminUsers; MeetingCreator role; new
-user; staging PostgreSQL/Redis.</v>
+        <v>1. AdminUsers.
+2. MeetingCreator role.
+3. New user.
+4. Staging PostgreSQL/Redis.</v>
       </c>
       <c r="F12" s="108" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="G12" s="109" t="str"/>
       <c r="H12" s="108" t="str"/>
@@ -4723,10 +4732,7 @@
       <c r="L12" s="108" t="str"/>
       <c r="M12" s="109" t="str"/>
       <c r="N12" s="108" t="str"/>
-      <c r="O12" s="110" t="str">
-        <v>frontend/src/features/acces
-s/UsersPage.tsx:1</v>
-      </c>
+      <c r="O12" s="110" t="str"/>
       <c r="P12"/>
     </row>
   </sheetData>
@@ -4808,7 +4814,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>Source-reviewed end-to-end workflow; record results only after execution.</v>
+        <v>System-level test flow: Draft, submission, rejection, revision and approval</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -4848,7 +4854,7 @@
       <c r="N4" s="97"/>
       <c r="O4" s="99"/>
       <c r="P4" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
     </row>
     <row r="5">
@@ -5063,33 +5069,32 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="128" customHeight="1">
+    <row r="12" ht="95.0" customHeight="1">
       <c r="A12" s="108" t="str">
         <v>SYS-02</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Draft, submission, rejection, revision
-and approval</v>
+        <v>Draft, submission, rejection, revision and approval</v>
       </c>
       <c r="C12" s="108" t="str">
         <v>1. Create and submit Draft.
-2. Read notification and reject with
-reason.
+2. Read notification and reject with reason.
 3. Revise and resubmit.
 4. Approve.
 5. Inspect history.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>Transitions/recipients are correct;
-reasons and history persist;
-unauthorized actions fail.</v>
+        <v>1. Transitions/recipients are correct.
+2. Reasons and history persist.
+3. Unauthorized actions fail.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>Separate active organizer/approver;
-ready meeting; notification worker.</v>
+        <v>1. Separate active organizer/approver.
+2. Ready meeting.
+3. Notification worker.</v>
       </c>
       <c r="F12" s="108" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="G12" s="109" t="str"/>
       <c r="H12" s="108" t="str"/>
@@ -5099,11 +5104,7 @@
       <c r="L12" s="108" t="str"/>
       <c r="M12" s="109" t="str"/>
       <c r="N12" s="108" t="str"/>
-      <c r="O12" s="110" t="str">
-        <v>frontend/src/features/meeti
-ngs/workflow/MeetingWorkflo
-wBar.tsx:1</v>
-      </c>
+      <c r="O12" s="110" t="str"/>
       <c r="P12"/>
     </row>
   </sheetData>
@@ -5185,7 +5186,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>Source-reviewed end-to-end workflow; record results only after execution.</v>
+        <v>System-level test flow: Publication, notifications, email and Calendar</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -5225,7 +5226,7 @@
       <c r="N4" s="97"/>
       <c r="O4" s="99"/>
       <c r="P4" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
     </row>
     <row r="5">
@@ -5440,13 +5441,12 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="92" customHeight="1">
+    <row r="12" ht="124.0" customHeight="1">
       <c r="A12" s="108" t="str">
         <v>SYS-03</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Publication, notifications, email and
-Calendar</v>
+        <v>Publication, notifications, email and Calendar</v>
       </c>
       <c r="C12" s="108" t="str">
         <v>1. Publish.
@@ -5455,18 +5455,19 @@
 4. Compare Calendar and details.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>Published status and schedule agree;
-intended recipients receive invitation;
-retries do not duplicate; outsiders
-receive no data.</v>
+        <v>1. Published status and schedule agree.
+2. Intended recipients receive invitation.
+3. Retries do not duplicate.
+4. Outsiders receive no data.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>Approved fixture with active
-Chair/Secretary and participants; seeded
-roster; SMTP sandbox; workers enabled.</v>
+        <v>1. Approved fixture with active Chair/Secretary and participants.
+2. Seeded roster.
+3. SMTP sandbox.
+4. Workers enabled.</v>
       </c>
       <c r="F12" s="108" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="G12" s="109" t="str"/>
       <c r="H12" s="108" t="str"/>
@@ -5476,11 +5477,7 @@
       <c r="L12" s="108" t="str"/>
       <c r="M12" s="109" t="str"/>
       <c r="N12" s="108" t="str"/>
-      <c r="O12" s="110" t="str">
-        <v>frontend/src/features/meeti
-ngs/workflow/MeetingWorkflo
-wBar.tsx:1</v>
-      </c>
+      <c r="O12" s="110" t="str"/>
       <c r="P12"/>
     </row>
   </sheetData>
@@ -5562,7 +5559,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>Source-reviewed end-to-end workflow; record results only after execution.</v>
+        <v>System-level test flow: Synchronize published meeting reschedule</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -5602,7 +5599,7 @@
       <c r="N4" s="97"/>
       <c r="O4" s="99"/>
       <c r="P4" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
     </row>
     <row r="5">
@@ -5817,7 +5814,7 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="110" customHeight="1">
+    <row r="12" ht="95.0" customHeight="1">
       <c r="A12" s="108" t="str">
         <v>SYS-04</v>
       </c>
@@ -5827,22 +5824,22 @@
       <c r="C12" s="108" t="str">
         <v>1. Reschedule.
 2. Inspect history.
-3. Check bell, update email and
-Calendar.
+3. Check bell, update email and Calendar.
 4. Reload both browsers.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>All screens show latest schedule;
-history records change; updates contain
-new time.</v>
+        <v>1. All screens show latest schedule.
+2. History records change.
+3. Updates contain new time.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>Published meeting; participants;
-original invitation recorded; SMTP
-sandbox.</v>
+        <v>1. Published meeting.
+2. Participants.
+3. Original invitation recorded.
+4. SMTP sandbox.</v>
       </c>
       <c r="F12" s="108" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="G12" s="109" t="str"/>
       <c r="H12" s="108" t="str"/>
@@ -5852,10 +5849,7 @@
       <c r="L12" s="108" t="str"/>
       <c r="M12" s="109" t="str"/>
       <c r="N12" s="108" t="str"/>
-      <c r="O12" s="110" t="str">
-        <v>frontend/src/features/meeti
-ngs/MeetingForm.tsx:1</v>
-      </c>
+      <c r="O12" s="110" t="str"/>
       <c r="P12"/>
     </row>
   </sheetData>
@@ -5937,7 +5931,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>Source-reviewed end-to-end workflow; record results only after execution.</v>
+        <v>System-level test flow: Deactivate, revoke sessions and restore access</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -5977,7 +5971,7 @@
       <c r="N4" s="97"/>
       <c r="O4" s="99"/>
       <c r="P4" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
     </row>
     <row r="5">
@@ -6192,13 +6186,12 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="92" customHeight="1">
+    <row r="12" ht="109.5" customHeight="1">
       <c r="A12" s="108" t="str">
         <v>SYS-05</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Deactivate, revoke sessions and restore
-access</v>
+        <v>Deactivate, revoke sessions and restore access</v>
       </c>
       <c r="C12" s="108" t="str">
         <v>1. Deactivate target.
@@ -6207,17 +6200,17 @@
 4. Sign in again.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>Operations fail while inactive; new
-sign-in succeeds after reactivation; old
-sessions cannot bypass active-user
-checks.</v>
+        <v>1. Operations fail while inactive.
+2. New sign-in succeeds after reactivation.
+3. Old sessions cannot bypass active-user checks.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>Independent admin; target signed in on
-two tabs; not final admin.</v>
+        <v>1. Independent admin.
+2. Target signed in on two tabs.
+3. Not final admin.</v>
       </c>
       <c r="F12" s="108" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="G12" s="109" t="str"/>
       <c r="H12" s="108" t="str"/>
@@ -6227,10 +6220,7 @@
       <c r="L12" s="108" t="str"/>
       <c r="M12" s="109" t="str"/>
       <c r="N12" s="108" t="str"/>
-      <c r="O12" s="110" t="str">
-        <v>frontend/src/features/acces
-s/UsersPage.tsx:1</v>
-      </c>
+      <c r="O12" s="110" t="str"/>
       <c r="P12"/>
     </row>
   </sheetData>
@@ -6312,7 +6302,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>Source-reviewed end-to-end workflow; record results only after execution.</v>
+        <v>System-level test flow: Reset password across email and authentication</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -6352,7 +6342,7 @@
       <c r="N4" s="97"/>
       <c r="O4" s="99"/>
       <c r="P4" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
     </row>
     <row r="5">
@@ -6567,33 +6557,33 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="128" customHeight="1">
+    <row r="12" ht="95.0" customHeight="1">
       <c r="A12" s="108" t="str">
         <v>SYS-06</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Reset password across email and
-authentication</v>
+        <v>Reset password across email and authentication</v>
       </c>
       <c r="C12" s="108" t="str">
         <v>1. Request reset.
 2. Complete through email.
 3. Try old/new passwords.
 4. Reuse token.
-5. Check old sessions against auth
-contract.</v>
+5. Check old sessions against auth contract.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>Old password fails; new one works; token
-is single-use; session revocation
-follows backend contract.</v>
+        <v>1. Old password fails.
+2. New one works.
+3. Token is single-use.
+4. Session revocation follows backend contract.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>Administrator/test user; SMTP sandbox;
-issued reset link.</v>
+        <v>1. Administrator/test user.
+2. SMTP sandbox.
+3. Issued reset link.</v>
       </c>
       <c r="F12" s="108" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="G12" s="109" t="str"/>
       <c r="H12" s="108" t="str"/>
@@ -6603,10 +6593,7 @@
       <c r="L12" s="108" t="str"/>
       <c r="M12" s="109" t="str"/>
       <c r="N12" s="108" t="str"/>
-      <c r="O12" s="110" t="str">
-        <v>frontend/src/features/auth/
-LoginPage.tsx:1</v>
-      </c>
+      <c r="O12" s="110" t="str"/>
       <c r="P12"/>
     </row>
   </sheetData>

--- a/docs/08-reports/test-reports/Report5.3_System_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.3_System_Test.xlsx
@@ -7,14 +7,15 @@
     <sheet name="Test Cases" sheetId="2" r:id="sheet2"/>
     <sheet name="Test Statistics" sheetId="3" r:id="sheet3"/>
     <sheet name="WorkFlow1" sheetId="4" r:id="sheet4"/>
-    <sheet name="WorkFlow2" sheetId="5" r:id="sheet5"/>
-    <sheet name="WorkFlow3" sheetId="6" r:id="sheet6"/>
-    <sheet name="WorkFlow4" sheetId="7" r:id="sheet7"/>
-    <sheet name="WorkFlow5" sheetId="8" r:id="sheet8"/>
-    <sheet name="WorkFlow6" sheetId="9" r:id="sheet9"/>
-    <sheet name="WorkFlow7" sheetId="10" r:id="sheet10"/>
-    <sheet name="WorkFlow8" sheetId="11" r:id="sheet11"/>
-    <sheet name="WorkFlow9" sheetId="12" r:id="sheet12"/>
+    <sheet name="WorkFlow10" sheetId="5" r:id="sheet5"/>
+    <sheet name="WorkFlow2" sheetId="6" r:id="sheet6"/>
+    <sheet name="WorkFlow3" sheetId="7" r:id="sheet7"/>
+    <sheet name="WorkFlow4" sheetId="8" r:id="sheet8"/>
+    <sheet name="WorkFlow5" sheetId="9" r:id="sheet9"/>
+    <sheet name="WorkFlow6" sheetId="10" r:id="sheet10"/>
+    <sheet name="WorkFlow7" sheetId="11" r:id="sheet11"/>
+    <sheet name="WorkFlow8" sheetId="12" r:id="sheet12"/>
+    <sheet name="WorkFlow9" sheetId="13" r:id="sheet13"/>
   </sheets>
   <calcPr fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1194,7 +1195,7 @@
         <v>Issue Date</v>
       </c>
       <c r="F5" s="14" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -1420,7 +1421,7 @@
     </row>
     <row r="12" ht="21.75" customHeight="1">
       <c r="A12" s="32" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="B12" s="26" t="str">
         <v>1.1</v>
@@ -1432,7 +1433,7 @@
         <v>M</v>
       </c>
       <c r="E12" s="29" t="str">
-        <v>Regenerate: 1099 xUnit methods</v>
+        <v>Regenerate: 1129 xUnit methods</v>
       </c>
       <c r="F12" s="33" t="str"/>
       <c r="G12" s="31"/>
@@ -1742,7 +1743,7 @@
         <v>Feature</v>
       </c>
       <c r="B2" s="101" t="str">
-        <v>Isolate meeting data across roles</v>
+        <v>Reset password across email and authentication</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -1766,7 +1767,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>System-level test flow: Isolate meeting data across roles</v>
+        <v>System-level test flow: Reset password across email and authentication</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -2003,7 +2004,7 @@
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="108" t="str">
-        <v>Isolate meeting data across roles</v>
+        <v>Reset password across email and authentication</v>
       </c>
       <c r="B11" s="108"/>
       <c r="C11" s="108"/>
@@ -2021,26 +2022,30 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="109.5" customHeight="1">
+    <row r="12" ht="95.0" customHeight="1">
       <c r="A12" s="108" t="str">
-        <v>SYS-07</v>
+        <v>SYS-06</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Isolate meeting data across roles</v>
+        <v>Reset password across email and authentication</v>
       </c>
       <c r="C12" s="108" t="str">
-        <v>1. Open list/details as each role.
-2. Try history, edit and transitions.
-3. Replace approver and retry as former approver.</v>
+        <v>1. Request reset.
+2. Complete through email.
+3. Try old/new passwords.
+4. Reuse token.
+5. Check old sessions against auth contract.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>1. Access follows relationship/state.
-2. Unrelated or revoked users cannot read restricted data.
-3. Inaccessible records return 404.</v>
+        <v>1. Old password fails.
+2. New one works.
+3. Token is single-use.
+4. Session revocation follows backend contract.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>1. Organizer, assigned approver, participant, outsider.
-2. Draft/WaitingApproval/Published fixtures.</v>
+        <v>1. Administrator/test user.
+2. SMTP sandbox.
+3. Issued reset link.</v>
       </c>
       <c r="F12" s="108" t="str">
         <v>Pending</v>
@@ -2111,7 +2116,7 @@
         <v>Feature</v>
       </c>
       <c r="B2" s="101" t="str">
-        <v>Recover queued email after SMTP outage</v>
+        <v>Isolate meeting data across roles</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -2135,7 +2140,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>System-level test flow: Recover queued email after SMTP outage</v>
+        <v>System-level test flow: Isolate meeting data across roles</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -2372,7 +2377,7 @@
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="108" t="str">
-        <v>Recover queued email after SMTP outage</v>
+        <v>Isolate meeting data across roles</v>
       </c>
       <c r="B11" s="108"/>
       <c r="C11" s="108"/>
@@ -2390,28 +2395,26 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="95.0" customHeight="1">
+    <row r="12" ht="109.5" customHeight="1">
       <c r="A12" s="108" t="str">
-        <v>SYS-08</v>
+        <v>SYS-07</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Recover queued email after SMTP outage</v>
+        <v>Isolate meeting data across roles</v>
       </c>
       <c r="C12" s="108" t="str">
-        <v>1. Stop SMTP.
-2. Publish.
-3. Inspect retry state.
-4. Restart SMTP and allow retry.
-5. Compare mail and queue.</v>
+        <v>1. Open list/details as each role.
+2. Try history, edit and transitions.
+3. Replace approver and retry as former approver.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>1. Publication persists.
-2. Email retries after recovery without duplicate deduplication keys.</v>
+        <v>1. Access follows relationship/state.
+2. Unrelated or revoked users cannot read restricted data.
+3. Inaccessible records return 404.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>1. Isolated staging.
-2. Controllable SMTP sandbox.
-3. Valid Approved fixture.</v>
+        <v>1. Organizer, assigned approver, participant, outsider.
+2. Draft/WaitingApproval/Published fixtures.</v>
       </c>
       <c r="F12" s="108" t="str">
         <v>Pending</v>
@@ -2482,6 +2485,377 @@
         <v>Feature</v>
       </c>
       <c r="B2" s="101" t="str">
+        <v>Recover queued email after SMTP outage</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="99"/>
+      <c r="P2" t="str">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="100" t="str">
+        <v>Test requirement</v>
+      </c>
+      <c r="B3" s="103" t="str">
+        <v>System-level test flow: Recover queued email after SMTP outage</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="99"/>
+      <c r="P3" t="str">
+        <v>Failed</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="100" t="str">
+        <v>Number of TCs</v>
+      </c>
+      <c r="B4" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
+      <c r="O4" s="99"/>
+      <c r="P4" t="str">
+        <v>Pending</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="105" t="str">
+        <v>Testing Round</v>
+      </c>
+      <c r="B5" s="105" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="C5" s="105" t="str">
+        <v>Failed</v>
+      </c>
+      <c r="D5" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="E5" s="105" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="99"/>
+      <c r="P5" t="str">
+        <v>Skipped</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="100" t="str">
+        <v>Round 1</v>
+      </c>
+      <c r="B6" s="105" t="n">
+        <f>COUNTIF(F12:F12,"Passed")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="105" t="n">
+        <f>COUNTIF(F12:F12,"Failed")</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="105" t="n">
+        <f>B4-B6-C6-E6</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="105" t="n">
+        <f>COUNTIF(F12:F12,"Skipped")</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="99"/>
+      <c r="P6"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="100" t="str">
+        <v>Round 2</v>
+      </c>
+      <c r="B7" s="105" t="n">
+        <f>COUNTIF(I12:I12,"Passed")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="105" t="n">
+        <f>COUNTIF(I12:I12,"Failed")</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="105" t="n">
+        <f>B4-B7-C7-E7</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="105" t="n">
+        <f>COUNTIF(I12:I12,"Skipped")</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="99"/>
+      <c r="P7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="100" t="str">
+        <v>Round 3</v>
+      </c>
+      <c r="B8" s="105" t="n">
+        <f>COUNTIF(L12:L12,"Passed")</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="105" t="n">
+        <f>COUNTIF(L12:L12,"Failed")</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="105" t="n">
+        <f>B4-B8-C8-E8</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="105" t="n">
+        <f>COUNTIF(L12:L12,"Skipped")</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="97"/>
+      <c r="K8" s="97"/>
+      <c r="L8" s="97"/>
+      <c r="M8" s="97"/>
+      <c r="N8" s="97"/>
+      <c r="O8" s="99"/>
+      <c r="P8"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="97"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="97"/>
+      <c r="K9" s="97"/>
+      <c r="L9" s="97"/>
+      <c r="M9" s="97"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="99"/>
+      <c r="P9"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="106" t="str">
+        <v>Test Case ID</v>
+      </c>
+      <c r="B10" s="106" t="str">
+        <v>Test Case Description</v>
+      </c>
+      <c r="C10" s="106" t="str">
+        <v>Test Case Procedure</v>
+      </c>
+      <c r="D10" s="106" t="str">
+        <v>Expected Results</v>
+      </c>
+      <c r="E10" s="106" t="str">
+        <v>Pre-conditions</v>
+      </c>
+      <c r="F10" s="106" t="str">
+        <v>Round 1</v>
+      </c>
+      <c r="G10" s="106" t="str">
+        <v>Test date</v>
+      </c>
+      <c r="H10" s="106" t="str">
+        <v>Tester</v>
+      </c>
+      <c r="I10" s="106" t="str">
+        <v>Round 2</v>
+      </c>
+      <c r="J10" s="106" t="str">
+        <v>Test date</v>
+      </c>
+      <c r="K10" s="106" t="str">
+        <v>Tester</v>
+      </c>
+      <c r="L10" s="106" t="str">
+        <v>Round 3</v>
+      </c>
+      <c r="M10" s="106" t="str">
+        <v>Test date</v>
+      </c>
+      <c r="N10" s="106" t="str">
+        <v>Tester</v>
+      </c>
+      <c r="O10" s="106" t="str">
+        <v>Note</v>
+      </c>
+      <c r="P10"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="108" t="str">
+        <v>Recover queued email after SMTP outage</v>
+      </c>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="109"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="109"/>
+      <c r="N11" s="108"/>
+      <c r="O11" s="110"/>
+      <c r="P11"/>
+    </row>
+    <row r="12" ht="95.0" customHeight="1">
+      <c r="A12" s="108" t="str">
+        <v>SYS-08</v>
+      </c>
+      <c r="B12" s="108" t="str">
+        <v>Recover queued email after SMTP outage</v>
+      </c>
+      <c r="C12" s="108" t="str">
+        <v>1. Stop SMTP.
+2. Publish.
+3. Inspect retry state.
+4. Restart SMTP and allow retry.
+5. Compare mail and queue.</v>
+      </c>
+      <c r="D12" s="108" t="str">
+        <v>1. Publication persists.
+2. Email retries after recovery without duplicate deduplication keys.</v>
+      </c>
+      <c r="E12" s="108" t="str">
+        <v>1. Isolated staging.
+2. Controllable SMTP sandbox.
+3. Valid Approved fixture.</v>
+      </c>
+      <c r="F12" s="108" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G12" s="109" t="str"/>
+      <c r="H12" s="108" t="str"/>
+      <c r="I12" s="108" t="str"/>
+      <c r="J12" s="109" t="str"/>
+      <c r="K12" s="108" t="str"/>
+      <c r="L12" s="108" t="str"/>
+      <c r="M12" s="109" t="str"/>
+      <c r="N12" s="108" t="str"/>
+      <c r="O12" s="110" t="str"/>
+      <c r="P12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A11:O11"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="39.5"/>
+    <col customWidth="1" min="3" max="3" width="35.63"/>
+    <col customWidth="1" min="4" max="4" width="27.88"/>
+    <col customWidth="1" min="5" max="5" width="36.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="97"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="98"/>
+      <c r="Y1" s="99"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="100" t="str">
+        <v>Feature</v>
+      </c>
+      <c r="B2" s="101" t="str">
         <v>Operate agenda through complete meeting UI</v>
       </c>
       <c r="C2" s="5"/>
@@ -3110,24 +3484,25 @@
       <c r="Y9" s="10"/>
       <c r="Z9" s="10"/>
     </row>
-    <row r="10" ht="66.0" customHeight="1">
+    <row r="10" ht="124.0" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="56" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="57" t="str">
-        <v>Draft, submission, rejection, revision and approval</v>
+        <v>Record an in-person meeting with the room mic through to the exported transcript</v>
       </c>
       <c r="D10" s="58" t="str">
-        <v>WorkFlow2</v>
+        <v>WorkFlow10</v>
       </c>
       <c r="E10" s="57" t="str">
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F10" s="59" t="str">
-        <v>1. Separate active organizer/approver.
-2. Ready meeting.
-3. Notification worker.</v>
+        <v>1. InProgress in-person meeting.
+2. Secretary laptop with microphone.
+3. Chair and member browsers.
+4. Speech worker and file storage on staging.</v>
       </c>
       <c r="G10" s="60"/>
       <c r="H10" s="10"/>
@@ -3150,25 +3525,24 @@
       <c r="Y10" s="10"/>
       <c r="Z10" s="10"/>
     </row>
-    <row r="11" ht="95.0" customHeight="1">
+    <row r="11" ht="66.0" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="56" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="57" t="str">
-        <v>Publication, notifications, email and Calendar</v>
+        <v>Draft, submission, rejection, revision and approval</v>
       </c>
       <c r="D11" s="58" t="str">
-        <v>WorkFlow3</v>
+        <v>WorkFlow2</v>
       </c>
       <c r="E11" s="57" t="str">
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F11" s="59" t="str">
-        <v>1. Approved fixture with active Chair/Secretary and participants.
-2. Seeded roster.
-3. SMTP sandbox.
-4. Workers enabled.</v>
+        <v>1. Separate active organizer/approver.
+2. Ready meeting.
+3. Notification worker.</v>
       </c>
       <c r="G11" s="60"/>
       <c r="H11" s="10"/>
@@ -3191,25 +3565,25 @@
       <c r="Y11" s="10"/>
       <c r="Z11" s="10"/>
     </row>
-    <row r="12" ht="80.5" customHeight="1">
+    <row r="12" ht="95.0" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="56" t="n">
         <v>4</v>
       </c>
       <c r="C12" s="57" t="str">
-        <v>Synchronize published meeting reschedule</v>
+        <v>Publication, notifications, email and Calendar</v>
       </c>
       <c r="D12" s="58" t="str">
-        <v>WorkFlow4</v>
+        <v>WorkFlow3</v>
       </c>
       <c r="E12" s="57" t="str">
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F12" s="59" t="str">
-        <v>1. Published meeting.
-2. Participants.
-3. Original invitation recorded.
-4. SMTP sandbox.</v>
+        <v>1. Approved fixture with active Chair/Secretary and participants.
+2. Seeded roster.
+3. SMTP sandbox.
+4. Workers enabled.</v>
       </c>
       <c r="G12" s="60"/>
       <c r="H12" s="10"/>
@@ -3232,24 +3606,25 @@
       <c r="Y12" s="10"/>
       <c r="Z12" s="10"/>
     </row>
-    <row r="13" ht="66.0" customHeight="1">
+    <row r="13" ht="80.5" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="56" t="n">
         <v>5</v>
       </c>
       <c r="C13" s="57" t="str">
-        <v>Deactivate, revoke sessions and restore access</v>
+        <v>Synchronize published meeting reschedule</v>
       </c>
       <c r="D13" s="58" t="str">
-        <v>WorkFlow5</v>
+        <v>WorkFlow4</v>
       </c>
       <c r="E13" s="57" t="str">
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F13" s="59" t="str">
-        <v>1. Independent admin.
-2. Target signed in on two tabs.
-3. Not final admin.</v>
+        <v>1. Published meeting.
+2. Participants.
+3. Original invitation recorded.
+4. SMTP sandbox.</v>
       </c>
       <c r="G13" s="60"/>
       <c r="H13" s="10"/>
@@ -3278,18 +3653,18 @@
         <v>6</v>
       </c>
       <c r="C14" s="57" t="str">
-        <v>Reset password across email and authentication</v>
+        <v>Deactivate, revoke sessions and restore access</v>
       </c>
       <c r="D14" s="58" t="str">
-        <v>WorkFlow6</v>
+        <v>WorkFlow5</v>
       </c>
       <c r="E14" s="57" t="str">
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F14" s="59" t="str">
-        <v>1. Administrator/test user.
-2. SMTP sandbox.
-3. Issued reset link.</v>
+        <v>1. Independent admin.
+2. Target signed in on two tabs.
+3. Not final admin.</v>
       </c>
       <c r="G14" s="60"/>
       <c r="H14" s="10"/>
@@ -3312,23 +3687,24 @@
       <c r="Y14" s="10"/>
       <c r="Z14" s="10"/>
     </row>
-    <row r="15" ht="80.5" customHeight="1">
+    <row r="15" ht="66.0" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="56" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="57" t="str">
-        <v>Isolate meeting data across roles</v>
+        <v>Reset password across email and authentication</v>
       </c>
       <c r="D15" s="58" t="str">
-        <v>WorkFlow7</v>
+        <v>WorkFlow6</v>
       </c>
       <c r="E15" s="57" t="str">
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F15" s="59" t="str">
-        <v>1. Organizer, assigned approver, participant, outsider.
-2. Draft/WaitingApproval/Published fixtures.</v>
+        <v>1. Administrator/test user.
+2. SMTP sandbox.
+3. Issued reset link.</v>
       </c>
       <c r="G15" s="60"/>
       <c r="H15" s="10"/>
@@ -3351,24 +3727,23 @@
       <c r="Y15" s="10"/>
       <c r="Z15" s="10"/>
     </row>
-    <row r="16" ht="66.0" customHeight="1">
+    <row r="16" ht="80.5" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="56" t="n">
         <v>8</v>
       </c>
       <c r="C16" s="57" t="str">
-        <v>Recover queued email after SMTP outage</v>
+        <v>Isolate meeting data across roles</v>
       </c>
       <c r="D16" s="58" t="str">
-        <v>WorkFlow8</v>
+        <v>WorkFlow7</v>
       </c>
       <c r="E16" s="57" t="str">
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F16" s="59" t="str">
-        <v>1. Isolated staging.
-2. Controllable SMTP sandbox.
-3. Valid Approved fixture.</v>
+        <v>1. Organizer, assigned approver, participant, outsider.
+2. Draft/WaitingApproval/Published fixtures.</v>
       </c>
       <c r="G16" s="60"/>
       <c r="H16" s="10"/>
@@ -3391,22 +3766,24 @@
       <c r="Y16" s="10"/>
       <c r="Z16" s="10"/>
     </row>
-    <row r="17" ht="51.5" customHeight="1">
+    <row r="17" ht="66.0" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="56" t="n">
         <v>9</v>
       </c>
       <c r="C17" s="57" t="str">
-        <v>Operate agenda through complete meeting UI</v>
+        <v>Recover queued email after SMTP outage</v>
       </c>
       <c r="D17" s="58" t="str">
-        <v>WorkFlow9</v>
+        <v>WorkFlow8</v>
       </c>
       <c r="E17" s="57" t="str">
         <v>1 definitions / scenarios</v>
       </c>
       <c r="F17" s="59" t="str">
-        <v>1. Blocked: agenda UI and meeting-start workflow unavailable in this checkout.</v>
+        <v>1. Isolated staging.
+2. Controllable SMTP sandbox.
+3. Valid Approved fixture.</v>
       </c>
       <c r="G17" s="60"/>
       <c r="H17" s="10"/>
@@ -3429,6 +3806,44 @@
       <c r="Y17" s="10"/>
       <c r="Z17" s="10"/>
     </row>
+    <row r="18" ht="51.5" customHeight="1">
+      <c r="A18" s="10"/>
+      <c r="B18" s="56" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="57" t="str">
+        <v>Operate agenda through complete meeting UI</v>
+      </c>
+      <c r="D18" s="58" t="str">
+        <v>WorkFlow9</v>
+      </c>
+      <c r="E18" s="57" t="str">
+        <v>1 definitions / scenarios</v>
+      </c>
+      <c r="F18" s="59" t="str">
+        <v>1. Blocked: agenda UI and meeting-start workflow unavailable in this checkout.</v>
+      </c>
+      <c r="G18" s="60"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B3:C3"/>
@@ -3440,14 +3855,15 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D9" location="'WorkFlow1'!A1" display="WorkFlow1"/>
-    <hyperlink ref="D10" location="'WorkFlow2'!A1" display="WorkFlow2"/>
-    <hyperlink ref="D11" location="'WorkFlow3'!A1" display="WorkFlow3"/>
-    <hyperlink ref="D12" location="'WorkFlow4'!A1" display="WorkFlow4"/>
-    <hyperlink ref="D13" location="'WorkFlow5'!A1" display="WorkFlow5"/>
-    <hyperlink ref="D14" location="'WorkFlow6'!A1" display="WorkFlow6"/>
-    <hyperlink ref="D15" location="'WorkFlow7'!A1" display="WorkFlow7"/>
-    <hyperlink ref="D16" location="'WorkFlow8'!A1" display="WorkFlow8"/>
-    <hyperlink ref="D17" location="'WorkFlow9'!A1" display="WorkFlow9"/>
+    <hyperlink ref="D10" location="'WorkFlow10'!A1" display="WorkFlow10"/>
+    <hyperlink ref="D11" location="'WorkFlow2'!A1" display="WorkFlow2"/>
+    <hyperlink ref="D12" location="'WorkFlow3'!A1" display="WorkFlow3"/>
+    <hyperlink ref="D13" location="'WorkFlow4'!A1" display="WorkFlow4"/>
+    <hyperlink ref="D14" location="'WorkFlow5'!A1" display="WorkFlow5"/>
+    <hyperlink ref="D15" location="'WorkFlow6'!A1" display="WorkFlow6"/>
+    <hyperlink ref="D16" location="'WorkFlow7'!A1" display="WorkFlow7"/>
+    <hyperlink ref="D17" location="'WorkFlow8'!A1" display="WorkFlow8"/>
+    <hyperlink ref="D18" location="'WorkFlow9'!A1" display="WorkFlow9"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.1506944444444445" footer="0.0" header="0.0" left="0.7479166666666667" right="0.7479166666666667" top="0.9840277777777778"/>
@@ -3617,7 +4033,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="71"/>
       <c r="H5" s="76" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
@@ -3847,26 +4263,26 @@
         <v>2</v>
       </c>
       <c r="C12" s="58" t="str">
-        <v>WorkFlow2</v>
+        <v>WorkFlow10</v>
       </c>
       <c r="D12" s="87" t="n">
-        <f>'WorkFlow2'!B6</f>
+        <f>'WorkFlow10'!B6</f>
         <v>0</v>
       </c>
       <c r="E12" s="87" t="n">
-        <f>'WorkFlow2'!C6</f>
+        <f>'WorkFlow10'!C6</f>
         <v>0</v>
       </c>
       <c r="F12" s="87" t="n">
-        <f>'WorkFlow2'!D6</f>
+        <f>'WorkFlow10'!D6</f>
         <v>1</v>
       </c>
       <c r="G12" s="87" t="n">
-        <f>'WorkFlow2'!E6</f>
+        <f>'WorkFlow10'!E6</f>
         <v>0</v>
       </c>
       <c r="H12" s="87" t="n">
-        <f>'WorkFlow2'!B4</f>
+        <f>'WorkFlow10'!B4</f>
         <v>1</v>
       </c>
       <c r="I12" s="10"/>
@@ -3894,26 +4310,26 @@
         <v>3</v>
       </c>
       <c r="C13" s="58" t="str">
-        <v>WorkFlow3</v>
+        <v>WorkFlow2</v>
       </c>
       <c r="D13" s="87" t="n">
-        <f>'WorkFlow3'!B6</f>
+        <f>'WorkFlow2'!B6</f>
         <v>0</v>
       </c>
       <c r="E13" s="87" t="n">
-        <f>'WorkFlow3'!C6</f>
+        <f>'WorkFlow2'!C6</f>
         <v>0</v>
       </c>
       <c r="F13" s="87" t="n">
-        <f>'WorkFlow3'!D6</f>
+        <f>'WorkFlow2'!D6</f>
         <v>1</v>
       </c>
       <c r="G13" s="87" t="n">
-        <f>'WorkFlow3'!E6</f>
+        <f>'WorkFlow2'!E6</f>
         <v>0</v>
       </c>
       <c r="H13" s="87" t="n">
-        <f>'WorkFlow3'!B4</f>
+        <f>'WorkFlow2'!B4</f>
         <v>1</v>
       </c>
       <c r="I13" s="10"/>
@@ -3941,26 +4357,26 @@
         <v>4</v>
       </c>
       <c r="C14" s="58" t="str">
-        <v>WorkFlow4</v>
+        <v>WorkFlow3</v>
       </c>
       <c r="D14" s="87" t="n">
-        <f>'WorkFlow4'!B6</f>
+        <f>'WorkFlow3'!B6</f>
         <v>0</v>
       </c>
       <c r="E14" s="87" t="n">
-        <f>'WorkFlow4'!C6</f>
+        <f>'WorkFlow3'!C6</f>
         <v>0</v>
       </c>
       <c r="F14" s="87" t="n">
-        <f>'WorkFlow4'!D6</f>
+        <f>'WorkFlow3'!D6</f>
         <v>1</v>
       </c>
       <c r="G14" s="87" t="n">
-        <f>'WorkFlow4'!E6</f>
+        <f>'WorkFlow3'!E6</f>
         <v>0</v>
       </c>
       <c r="H14" s="87" t="n">
-        <f>'WorkFlow4'!B4</f>
+        <f>'WorkFlow3'!B4</f>
         <v>1</v>
       </c>
       <c r="I14" s="10"/>
@@ -3988,26 +4404,26 @@
         <v>5</v>
       </c>
       <c r="C15" s="58" t="str">
-        <v>WorkFlow5</v>
+        <v>WorkFlow4</v>
       </c>
       <c r="D15" s="87" t="n">
-        <f>'WorkFlow5'!B6</f>
+        <f>'WorkFlow4'!B6</f>
         <v>0</v>
       </c>
       <c r="E15" s="87" t="n">
-        <f>'WorkFlow5'!C6</f>
+        <f>'WorkFlow4'!C6</f>
         <v>0</v>
       </c>
       <c r="F15" s="87" t="n">
-        <f>'WorkFlow5'!D6</f>
+        <f>'WorkFlow4'!D6</f>
         <v>1</v>
       </c>
       <c r="G15" s="87" t="n">
-        <f>'WorkFlow5'!E6</f>
+        <f>'WorkFlow4'!E6</f>
         <v>0</v>
       </c>
       <c r="H15" s="87" t="n">
-        <f>'WorkFlow5'!B4</f>
+        <f>'WorkFlow4'!B4</f>
         <v>1</v>
       </c>
       <c r="I15" s="10"/>
@@ -4035,26 +4451,26 @@
         <v>6</v>
       </c>
       <c r="C16" s="58" t="str">
-        <v>WorkFlow6</v>
+        <v>WorkFlow5</v>
       </c>
       <c r="D16" s="87" t="n">
-        <f>'WorkFlow6'!B6</f>
+        <f>'WorkFlow5'!B6</f>
         <v>0</v>
       </c>
       <c r="E16" s="87" t="n">
-        <f>'WorkFlow6'!C6</f>
+        <f>'WorkFlow5'!C6</f>
         <v>0</v>
       </c>
       <c r="F16" s="87" t="n">
-        <f>'WorkFlow6'!D6</f>
+        <f>'WorkFlow5'!D6</f>
         <v>1</v>
       </c>
       <c r="G16" s="87" t="n">
-        <f>'WorkFlow6'!E6</f>
+        <f>'WorkFlow5'!E6</f>
         <v>0</v>
       </c>
       <c r="H16" s="87" t="n">
-        <f>'WorkFlow6'!B4</f>
+        <f>'WorkFlow5'!B4</f>
         <v>1</v>
       </c>
       <c r="I16" s="10"/>
@@ -4082,26 +4498,26 @@
         <v>7</v>
       </c>
       <c r="C17" s="58" t="str">
-        <v>WorkFlow7</v>
+        <v>WorkFlow6</v>
       </c>
       <c r="D17" s="87" t="n">
-        <f>'WorkFlow7'!B6</f>
+        <f>'WorkFlow6'!B6</f>
         <v>0</v>
       </c>
       <c r="E17" s="87" t="n">
-        <f>'WorkFlow7'!C6</f>
+        <f>'WorkFlow6'!C6</f>
         <v>0</v>
       </c>
       <c r="F17" s="87" t="n">
-        <f>'WorkFlow7'!D6</f>
+        <f>'WorkFlow6'!D6</f>
         <v>1</v>
       </c>
       <c r="G17" s="87" t="n">
-        <f>'WorkFlow7'!E6</f>
+        <f>'WorkFlow6'!E6</f>
         <v>0</v>
       </c>
       <c r="H17" s="87" t="n">
-        <f>'WorkFlow7'!B4</f>
+        <f>'WorkFlow6'!B4</f>
         <v>1</v>
       </c>
       <c r="I17" s="10"/>
@@ -4129,26 +4545,26 @@
         <v>8</v>
       </c>
       <c r="C18" s="58" t="str">
-        <v>WorkFlow8</v>
+        <v>WorkFlow7</v>
       </c>
       <c r="D18" s="87" t="n">
-        <f>'WorkFlow8'!B6</f>
+        <f>'WorkFlow7'!B6</f>
         <v>0</v>
       </c>
       <c r="E18" s="87" t="n">
-        <f>'WorkFlow8'!C6</f>
+        <f>'WorkFlow7'!C6</f>
         <v>0</v>
       </c>
       <c r="F18" s="87" t="n">
-        <f>'WorkFlow8'!D6</f>
+        <f>'WorkFlow7'!D6</f>
         <v>1</v>
       </c>
       <c r="G18" s="87" t="n">
-        <f>'WorkFlow8'!E6</f>
+        <f>'WorkFlow7'!E6</f>
         <v>0</v>
       </c>
       <c r="H18" s="87" t="n">
-        <f>'WorkFlow8'!B4</f>
+        <f>'WorkFlow7'!B4</f>
         <v>1</v>
       </c>
       <c r="I18" s="10"/>
@@ -4176,26 +4592,26 @@
         <v>9</v>
       </c>
       <c r="C19" s="58" t="str">
-        <v>WorkFlow9</v>
+        <v>WorkFlow8</v>
       </c>
       <c r="D19" s="87" t="n">
-        <f>'WorkFlow9'!B6</f>
+        <f>'WorkFlow8'!B6</f>
         <v>0</v>
       </c>
       <c r="E19" s="87" t="n">
-        <f>'WorkFlow9'!C6</f>
+        <f>'WorkFlow8'!C6</f>
         <v>0</v>
       </c>
       <c r="F19" s="87" t="n">
-        <f>'WorkFlow9'!D6</f>
+        <f>'WorkFlow8'!D6</f>
         <v>1</v>
       </c>
       <c r="G19" s="87" t="n">
-        <f>'WorkFlow9'!E6</f>
+        <f>'WorkFlow8'!E6</f>
         <v>0</v>
       </c>
       <c r="H19" s="87" t="n">
-        <f>'WorkFlow9'!B4</f>
+        <f>'WorkFlow8'!B4</f>
         <v>1</v>
       </c>
       <c r="I19" s="10"/>
@@ -4217,31 +4633,33 @@
       <c r="Y19" s="10"/>
       <c r="Z19" s="10"/>
     </row>
-    <row r="20" ht="25" customHeight="1">
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="80"/>
-      <c r="B20" s="88"/>
-      <c r="C20" s="89" t="str">
-        <v>Sub total</v>
-      </c>
-      <c r="D20" s="90" t="n">
-        <f>SUM(D11:D19)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="90" t="n">
-        <f>SUM(E11:E19)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="90" t="n">
-        <f>SUM(F11:F19)</f>
-        <v>9</v>
-      </c>
-      <c r="G20" s="90" t="n">
-        <f>SUM(G11:G19)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="91" t="n">
-        <f>SUM(H11:H19)</f>
-        <v>9</v>
+      <c r="B20" s="86" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="58" t="str">
+        <v>WorkFlow9</v>
+      </c>
+      <c r="D20" s="87" t="n">
+        <f>'WorkFlow9'!B6</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="87" t="n">
+        <f>'WorkFlow9'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="87" t="n">
+        <f>'WorkFlow9'!D6</f>
+        <v>1</v>
+      </c>
+      <c r="G20" s="87" t="n">
+        <f>'WorkFlow9'!E6</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="87" t="n">
+        <f>'WorkFlow9'!B4</f>
+        <v>1</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
@@ -4262,60 +4680,70 @@
       <c r="Y20" s="10"/>
       <c r="Z20" s="10"/>
     </row>
-    <row r="21">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="8" t="str">
-        <v>Test coverage</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="95" t="n">
-        <f>IFERROR((D20+E20)*100/(H20-G20),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="F22" s="10" t="str">
-        <v>%</v>
-      </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
-      <c r="U22" s="10"/>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="10"/>
-      <c r="Y22" s="10"/>
-      <c r="Z22" s="10"/>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="80"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="89" t="str">
+        <v>Sub total</v>
+      </c>
+      <c r="D21" s="90" t="n">
+        <f>SUM(D11:D20)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="90" t="n">
+        <f>SUM(E11:E20)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="90" t="n">
+        <f>SUM(F11:F20)</f>
+        <v>10</v>
+      </c>
+      <c r="G21" s="90" t="n">
+        <f>SUM(G11:G20)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="91" t="n">
+        <f>SUM(H11:H20)</f>
+        <v>10</v>
+      </c>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
+    </row>
+    <row r="22">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="8" t="str">
-        <v>Test successful coverage</v>
+        <v>Test coverage</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="95" t="n">
-        <f>IFERROR(D20*100/(H20-G20),0)</f>
+        <f>IFERROR((D21+E21)*100/(H21-G21),0)</f>
         <v>0.0</v>
       </c>
       <c r="F23" s="10" t="str">
@@ -4342,6 +4770,41 @@
       <c r="Y23" s="10"/>
       <c r="Z23" s="10"/>
     </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="8" t="str">
+        <v>Test successful coverage</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="95" t="n">
+        <f>IFERROR(D21*100/(H21-G21),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F24" s="10" t="str">
+        <v>%</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B1:H1"/>
@@ -4355,14 +4818,15 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C11" location="'WorkFlow1'!A1" display="WorkFlow1"/>
-    <hyperlink ref="C12" location="'WorkFlow2'!A1" display="WorkFlow2"/>
-    <hyperlink ref="C13" location="'WorkFlow3'!A1" display="WorkFlow3"/>
-    <hyperlink ref="C14" location="'WorkFlow4'!A1" display="WorkFlow4"/>
-    <hyperlink ref="C15" location="'WorkFlow5'!A1" display="WorkFlow5"/>
-    <hyperlink ref="C16" location="'WorkFlow6'!A1" display="WorkFlow6"/>
-    <hyperlink ref="C17" location="'WorkFlow7'!A1" display="WorkFlow7"/>
-    <hyperlink ref="C18" location="'WorkFlow8'!A1" display="WorkFlow8"/>
-    <hyperlink ref="C19" location="'WorkFlow9'!A1" display="WorkFlow9"/>
+    <hyperlink ref="C12" location="'WorkFlow10'!A1" display="WorkFlow10"/>
+    <hyperlink ref="C13" location="'WorkFlow2'!A1" display="WorkFlow2"/>
+    <hyperlink ref="C14" location="'WorkFlow3'!A1" display="WorkFlow3"/>
+    <hyperlink ref="C15" location="'WorkFlow4'!A1" display="WorkFlow4"/>
+    <hyperlink ref="C16" location="'WorkFlow5'!A1" display="WorkFlow5"/>
+    <hyperlink ref="C17" location="'WorkFlow6'!A1" display="WorkFlow6"/>
+    <hyperlink ref="C18" location="'WorkFlow7'!A1" display="WorkFlow7"/>
+    <hyperlink ref="C19" location="'WorkFlow8'!A1" display="WorkFlow8"/>
+    <hyperlink ref="C20" location="'WorkFlow9'!A1" display="WorkFlow9"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.9840277777777777" footer="0.0" header="0.0" left="0.7479166666666667" right="0.7479166666666667" top="0.9840277777777778"/>
@@ -4790,7 +5254,7 @@
         <v>Feature</v>
       </c>
       <c r="B2" s="101" t="str">
-        <v>Draft, submission, rejection, revision and approval</v>
+        <v>Record an in-person meeting with the room mic through to the exported transcript</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -4814,7 +5278,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>System-level test flow: Draft, submission, rejection, revision and approval</v>
+        <v>System-level test flow: Record an in-person meeting with the room mic through to the exported transcript</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -5051,7 +5515,7 @@
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="108" t="str">
-        <v>Draft, submission, rejection, revision and approval</v>
+        <v>Record an in-person meeting with the room mic through to the exported transcript</v>
       </c>
       <c r="B11" s="108"/>
       <c r="C11" s="108"/>
@@ -5069,29 +5533,33 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="95.0" customHeight="1">
+    <row r="12" ht="196.5" customHeight="1">
       <c r="A12" s="108" t="str">
-        <v>SYS-02</v>
+        <v>SYS-10</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Draft, submission, rejection, revision and approval</v>
+        <v>Record an in-person meeting with the room mic through to the exported transcript</v>
       </c>
       <c r="C12" s="108" t="str">
-        <v>1. Create and submit Draft.
-2. Read notification and reject with reason.
-3. Revise and resubmit.
-4. Approve.
-5. Inspect history.</v>
+        <v>1. Secretary switches the room mic on with consent and records two takes.
+2. Member watches the Bản ghi tab while recording.
+3. Wait for the transcript; name the speakers and correct one line.
+4. Delete one take.
+5. Chair downloads the audio and the transcript (.txt).
+6. Repeat the download on a Mật meeting.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>1. Transitions/recipients are correct.
-2. Reasons and history persist.
-3. Unauthorized actions fail.</v>
+        <v>1. Takes form one room recording transcribed as a whole.
+2. Deleting a take removes its sound and lines and keeps edits and names.
+3. Only Chair/Secretary download.
+4. A Mật meeting allows no download.
+5. Audit records each step.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>1. Separate active organizer/approver.
-2. Ready meeting.
-3. Notification worker.</v>
+        <v>1. InProgress in-person meeting.
+2. Secretary laptop with microphone.
+3. Chair and member browsers.
+4. Speech worker and file storage on staging.</v>
       </c>
       <c r="F12" s="108" t="str">
         <v>Pending</v>
@@ -5162,7 +5630,7 @@
         <v>Feature</v>
       </c>
       <c r="B2" s="101" t="str">
-        <v>Publication, notifications, email and Calendar</v>
+        <v>Draft, submission, rejection, revision and approval</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -5186,7 +5654,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>System-level test flow: Publication, notifications, email and Calendar</v>
+        <v>System-level test flow: Draft, submission, rejection, revision and approval</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -5423,7 +5891,7 @@
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="108" t="str">
-        <v>Publication, notifications, email and Calendar</v>
+        <v>Draft, submission, rejection, revision and approval</v>
       </c>
       <c r="B11" s="108"/>
       <c r="C11" s="108"/>
@@ -5441,30 +5909,29 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="124.0" customHeight="1">
+    <row r="12" ht="95.0" customHeight="1">
       <c r="A12" s="108" t="str">
-        <v>SYS-03</v>
+        <v>SYS-02</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Publication, notifications, email and Calendar</v>
+        <v>Draft, submission, rejection, revision and approval</v>
       </c>
       <c r="C12" s="108" t="str">
-        <v>1. Publish.
-2. Receive notification and ICS email.
-3. Follow notification.
-4. Compare Calendar and details.</v>
+        <v>1. Create and submit Draft.
+2. Read notification and reject with reason.
+3. Revise and resubmit.
+4. Approve.
+5. Inspect history.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>1. Published status and schedule agree.
-2. Intended recipients receive invitation.
-3. Retries do not duplicate.
-4. Outsiders receive no data.</v>
+        <v>1. Transitions/recipients are correct.
+2. Reasons and history persist.
+3. Unauthorized actions fail.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>1. Approved fixture with active Chair/Secretary and participants.
-2. Seeded roster.
-3. SMTP sandbox.
-4. Workers enabled.</v>
+        <v>1. Separate active organizer/approver.
+2. Ready meeting.
+3. Notification worker.</v>
       </c>
       <c r="F12" s="108" t="str">
         <v>Pending</v>
@@ -5535,7 +6002,7 @@
         <v>Feature</v>
       </c>
       <c r="B2" s="101" t="str">
-        <v>Synchronize published meeting reschedule</v>
+        <v>Publication, notifications, email and Calendar</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -5559,7 +6026,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>System-level test flow: Synchronize published meeting reschedule</v>
+        <v>System-level test flow: Publication, notifications, email and Calendar</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -5796,7 +6263,7 @@
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="108" t="str">
-        <v>Synchronize published meeting reschedule</v>
+        <v>Publication, notifications, email and Calendar</v>
       </c>
       <c r="B11" s="108"/>
       <c r="C11" s="108"/>
@@ -5814,29 +6281,30 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="95.0" customHeight="1">
+    <row r="12" ht="124.0" customHeight="1">
       <c r="A12" s="108" t="str">
-        <v>SYS-04</v>
+        <v>SYS-03</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Synchronize published meeting reschedule</v>
+        <v>Publication, notifications, email and Calendar</v>
       </c>
       <c r="C12" s="108" t="str">
-        <v>1. Reschedule.
-2. Inspect history.
-3. Check bell, update email and Calendar.
-4. Reload both browsers.</v>
+        <v>1. Publish.
+2. Receive notification and ICS email.
+3. Follow notification.
+4. Compare Calendar and details.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>1. All screens show latest schedule.
-2. History records change.
-3. Updates contain new time.</v>
+        <v>1. Published status and schedule agree.
+2. Intended recipients receive invitation.
+3. Retries do not duplicate.
+4. Outsiders receive no data.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>1. Published meeting.
-2. Participants.
-3. Original invitation recorded.
-4. SMTP sandbox.</v>
+        <v>1. Approved fixture with active Chair/Secretary and participants.
+2. Seeded roster.
+3. SMTP sandbox.
+4. Workers enabled.</v>
       </c>
       <c r="F12" s="108" t="str">
         <v>Pending</v>
@@ -5907,7 +6375,7 @@
         <v>Feature</v>
       </c>
       <c r="B2" s="101" t="str">
-        <v>Deactivate, revoke sessions and restore access</v>
+        <v>Synchronize published meeting reschedule</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -5931,7 +6399,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>System-level test flow: Deactivate, revoke sessions and restore access</v>
+        <v>System-level test flow: Synchronize published meeting reschedule</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -6168,7 +6636,7 @@
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="108" t="str">
-        <v>Deactivate, revoke sessions and restore access</v>
+        <v>Synchronize published meeting reschedule</v>
       </c>
       <c r="B11" s="108"/>
       <c r="C11" s="108"/>
@@ -6186,28 +6654,29 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="109.5" customHeight="1">
+    <row r="12" ht="95.0" customHeight="1">
       <c r="A12" s="108" t="str">
-        <v>SYS-05</v>
+        <v>SYS-04</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Deactivate, revoke sessions and restore access</v>
+        <v>Synchronize published meeting reschedule</v>
       </c>
       <c r="C12" s="108" t="str">
-        <v>1. Deactivate target.
-2. Try reading/editing from both tabs.
-3. Reactivate.
-4. Sign in again.</v>
+        <v>1. Reschedule.
+2. Inspect history.
+3. Check bell, update email and Calendar.
+4. Reload both browsers.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>1. Operations fail while inactive.
-2. New sign-in succeeds after reactivation.
-3. Old sessions cannot bypass active-user checks.</v>
+        <v>1. All screens show latest schedule.
+2. History records change.
+3. Updates contain new time.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>1. Independent admin.
-2. Target signed in on two tabs.
-3. Not final admin.</v>
+        <v>1. Published meeting.
+2. Participants.
+3. Original invitation recorded.
+4. SMTP sandbox.</v>
       </c>
       <c r="F12" s="108" t="str">
         <v>Pending</v>
@@ -6278,7 +6747,7 @@
         <v>Feature</v>
       </c>
       <c r="B2" s="101" t="str">
-        <v>Reset password across email and authentication</v>
+        <v>Deactivate, revoke sessions and restore access</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -6302,7 +6771,7 @@
         <v>Test requirement</v>
       </c>
       <c r="B3" s="103" t="str">
-        <v>System-level test flow: Reset password across email and authentication</v>
+        <v>System-level test flow: Deactivate, revoke sessions and restore access</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -6539,7 +7008,7 @@
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="108" t="str">
-        <v>Reset password across email and authentication</v>
+        <v>Deactivate, revoke sessions and restore access</v>
       </c>
       <c r="B11" s="108"/>
       <c r="C11" s="108"/>
@@ -6557,30 +7026,28 @@
       <c r="O11" s="110"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="95.0" customHeight="1">
+    <row r="12" ht="109.5" customHeight="1">
       <c r="A12" s="108" t="str">
-        <v>SYS-06</v>
+        <v>SYS-05</v>
       </c>
       <c r="B12" s="108" t="str">
-        <v>Reset password across email and authentication</v>
+        <v>Deactivate, revoke sessions and restore access</v>
       </c>
       <c r="C12" s="108" t="str">
-        <v>1. Request reset.
-2. Complete through email.
-3. Try old/new passwords.
-4. Reuse token.
-5. Check old sessions against auth contract.</v>
+        <v>1. Deactivate target.
+2. Try reading/editing from both tabs.
+3. Reactivate.
+4. Sign in again.</v>
       </c>
       <c r="D12" s="108" t="str">
-        <v>1. Old password fails.
-2. New one works.
-3. Token is single-use.
-4. Session revocation follows backend contract.</v>
+        <v>1. Operations fail while inactive.
+2. New sign-in succeeds after reactivation.
+3. Old sessions cannot bypass active-user checks.</v>
       </c>
       <c r="E12" s="108" t="str">
-        <v>1. Administrator/test user.
-2. SMTP sandbox.
-3. Issued reset link.</v>
+        <v>1. Independent admin.
+2. Target signed in on two tabs.
+3. Not final admin.</v>
       </c>
       <c r="F12" s="108" t="str">
         <v>Pending</v>

--- a/docs/08-reports/test-reports/Report5.3_System_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.3_System_Test.xlsx
@@ -32,62 +32,61 @@
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="MS PGothic"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="26.0"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="20.0"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font/>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FF993300"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF008000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="12.0"/>
@@ -98,72 +97,72 @@
       <b/>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <u/>
       <sz val="11.0"/>
       <color rgb="FF0000FF"/>
-      <name val="MS PGothic"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FF0000FF"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="MS PGothic"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="8">
@@ -893,14 +892,14 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="MS PGothic"/>
-        <a:ea typeface="MS PGothic"/>
-        <a:cs typeface="MS PGothic"/>
+        <a:latin typeface="Times New Roman"/>
+        <a:ea typeface="Times New Roman"/>
+        <a:cs typeface="Times New Roman"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="MS PGothic"/>
-        <a:ea typeface="MS PGothic"/>
-        <a:cs typeface="MS PGothic"/>
+        <a:latin typeface="Times New Roman"/>
+        <a:ea typeface="Times New Roman"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
